--- a/FinalSheet.xlsx
+++ b/FinalSheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nehakotha/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nehakotha/GASP-Clean-Air-Fund/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DFFF00-1F0F-4B47-B7CA-F4F1D75E2003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C79A08-BCA3-F044-8390-49A5E4EF578C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6880" yWindow="760" windowWidth="23360" windowHeight="16300" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="65">
   <si>
     <t>Year</t>
   </si>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>CCAC Allegheny Campus, CCAC North Campus, CCAC Boyce Campus, CCAC South Campus</t>
+  </si>
+  <si>
+    <t>Project Description</t>
+  </si>
+  <si>
+    <t>…..</t>
   </si>
 </sst>
 </file>
@@ -726,7 +732,8 @@
     <col min="4" max="4" width="28.1640625" customWidth="1"/>
     <col min="5" max="5" width="27.6640625" customWidth="1"/>
     <col min="6" max="6" width="54" style="4" customWidth="1"/>
-    <col min="7" max="7" width="41.6640625" customWidth="1"/>
+    <col min="7" max="7" width="63.33203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
     <col min="9" max="9" width="39.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -752,6 +759,9 @@
       <c r="G1" t="s">
         <v>41</v>
       </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
@@ -775,6 +785,9 @@
       <c r="G2" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="H2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
@@ -798,6 +811,9 @@
       <c r="G3" s="15" t="s">
         <v>22</v>
       </c>
+      <c r="H3" t="s">
+        <v>64</v>
+      </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -822,6 +838,9 @@
       <c r="G4" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="H4" t="s">
+        <v>64</v>
+      </c>
       <c r="I4" s="21"/>
     </row>
     <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -846,6 +865,9 @@
       <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
+      <c r="H5" t="s">
+        <v>64</v>
+      </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -870,6 +892,9 @@
       <c r="G6" s="15" t="s">
         <v>43</v>
       </c>
+      <c r="H6" t="s">
+        <v>64</v>
+      </c>
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -894,6 +919,9 @@
       <c r="G7" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -918,6 +946,9 @@
       <c r="G8" s="15" t="s">
         <v>9</v>
       </c>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -942,6 +973,9 @@
       <c r="G9" s="15" t="s">
         <v>24</v>
       </c>
+      <c r="H9" t="s">
+        <v>64</v>
+      </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -966,6 +1000,9 @@
       <c r="G10" s="15" t="s">
         <v>25</v>
       </c>
+      <c r="H10" t="s">
+        <v>64</v>
+      </c>
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -990,6 +1027,9 @@
       <c r="G11" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="H11" t="s">
+        <v>64</v>
+      </c>
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1014,6 +1054,9 @@
       <c r="G12" s="15" t="s">
         <v>26</v>
       </c>
+      <c r="H12" t="s">
+        <v>64</v>
+      </c>
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1038,6 +1081,9 @@
       <c r="G13" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="H13" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
@@ -1061,6 +1107,9 @@
       <c r="G14" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="H14" t="s">
+        <v>64</v>
+      </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1085,6 +1134,9 @@
       <c r="G15" s="15" t="s">
         <v>7</v>
       </c>
+      <c r="H15" t="s">
+        <v>64</v>
+      </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1109,6 +1161,9 @@
       <c r="G16" s="15" t="s">
         <v>9</v>
       </c>
+      <c r="H16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
@@ -1132,6 +1187,9 @@
       <c r="G17" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H17" t="s">
+        <v>64</v>
+      </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1156,6 +1214,9 @@
       <c r="G18" s="16" t="s">
         <v>59</v>
       </c>
+      <c r="H18" t="s">
+        <v>64</v>
+      </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1180,6 +1241,9 @@
       <c r="G19" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H19" t="s">
+        <v>64</v>
+      </c>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1204,6 +1268,9 @@
       <c r="G20" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H20" t="s">
+        <v>64</v>
+      </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1228,6 +1295,9 @@
       <c r="G21" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H21" t="s">
+        <v>64</v>
+      </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1252,6 +1322,9 @@
       <c r="G22" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H22" t="s">
+        <v>64</v>
+      </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1276,6 +1349,9 @@
       <c r="G23" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H23" t="s">
+        <v>64</v>
+      </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1300,6 +1376,9 @@
       <c r="G24" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H24" t="s">
+        <v>64</v>
+      </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1324,6 +1403,9 @@
       <c r="G25" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H25" t="s">
+        <v>64</v>
+      </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1348,6 +1430,9 @@
       <c r="G26" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H26" t="s">
+        <v>64</v>
+      </c>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1372,6 +1457,9 @@
       <c r="G27" s="16" t="s">
         <v>59</v>
       </c>
+      <c r="H27" t="s">
+        <v>64</v>
+      </c>
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1396,6 +1484,9 @@
       <c r="G28" s="6" t="s">
         <v>44</v>
       </c>
+      <c r="H28" t="s">
+        <v>64</v>
+      </c>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1420,6 +1511,9 @@
       <c r="G29" s="15" t="s">
         <v>28</v>
       </c>
+      <c r="H29" t="s">
+        <v>64</v>
+      </c>
       <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1444,6 +1538,9 @@
       <c r="G30" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="H30" t="s">
+        <v>64</v>
+      </c>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1468,6 +1565,9 @@
       <c r="G31" s="14" t="s">
         <v>4</v>
       </c>
+      <c r="H31" t="s">
+        <v>64</v>
+      </c>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1492,6 +1592,9 @@
       <c r="G32" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="H32" t="s">
+        <v>64</v>
+      </c>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1516,6 +1619,9 @@
       <c r="G33" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="H33" t="s">
+        <v>64</v>
+      </c>
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1540,6 +1646,9 @@
       <c r="G34" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H34" t="s">
+        <v>64</v>
+      </c>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1564,6 +1673,9 @@
       <c r="G35" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H35" t="s">
+        <v>64</v>
+      </c>
       <c r="I35" s="5"/>
     </row>
     <row r="36" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1588,6 +1700,9 @@
       <c r="G36" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H36" t="s">
+        <v>64</v>
+      </c>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1612,6 +1727,9 @@
       <c r="G37" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H37" t="s">
+        <v>64</v>
+      </c>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1636,6 +1754,9 @@
       <c r="G38" s="15" t="s">
         <v>29</v>
       </c>
+      <c r="H38" t="s">
+        <v>64</v>
+      </c>
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1660,6 +1781,9 @@
       <c r="G39" s="15" t="s">
         <v>30</v>
       </c>
+      <c r="H39" t="s">
+        <v>64</v>
+      </c>
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1684,6 +1808,9 @@
       <c r="G40" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H40" t="s">
+        <v>64</v>
+      </c>
       <c r="I40" s="5"/>
     </row>
     <row r="41" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1708,6 +1835,9 @@
       <c r="G41" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H41" t="s">
+        <v>64</v>
+      </c>
       <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1732,6 +1862,9 @@
       <c r="G42" s="15" t="s">
         <v>46</v>
       </c>
+      <c r="H42" t="s">
+        <v>64</v>
+      </c>
       <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1756,6 +1889,9 @@
       <c r="G43" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H43" t="s">
+        <v>64</v>
+      </c>
       <c r="I43" s="5"/>
     </row>
     <row r="44" spans="1:9" ht="51" x14ac:dyDescent="0.2">
@@ -1780,6 +1916,9 @@
       <c r="G44" s="15" t="s">
         <v>22</v>
       </c>
+      <c r="H44" t="s">
+        <v>64</v>
+      </c>
       <c r="I44" s="5"/>
     </row>
     <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1804,6 +1943,9 @@
       <c r="G45" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="H45" t="s">
+        <v>64</v>
+      </c>
       <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1828,6 +1970,9 @@
       <c r="G46" s="15" t="s">
         <v>31</v>
       </c>
+      <c r="H46" t="s">
+        <v>64</v>
+      </c>
       <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1852,6 +1997,9 @@
       <c r="G47" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="H47" t="s">
+        <v>64</v>
+      </c>
       <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1876,6 +2024,9 @@
       <c r="G48" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="H48" t="s">
+        <v>64</v>
+      </c>
       <c r="I48" s="5"/>
     </row>
     <row r="49" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1900,6 +2051,9 @@
       <c r="G49" s="14" t="s">
         <v>4</v>
       </c>
+      <c r="H49" t="s">
+        <v>64</v>
+      </c>
       <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1924,6 +2078,9 @@
       <c r="G50" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="H50" t="s">
+        <v>64</v>
+      </c>
       <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1948,6 +2105,9 @@
       <c r="G51" s="15" t="s">
         <v>32</v>
       </c>
+      <c r="H51" t="s">
+        <v>64</v>
+      </c>
       <c r="I51" s="23"/>
     </row>
     <row r="52" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1972,6 +2132,9 @@
       <c r="G52" s="16" t="s">
         <v>59</v>
       </c>
+      <c r="H52" t="s">
+        <v>64</v>
+      </c>
       <c r="I52" s="23"/>
     </row>
     <row r="53" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1996,6 +2159,9 @@
       <c r="G53" s="14" t="s">
         <v>49</v>
       </c>
+      <c r="H53" t="s">
+        <v>64</v>
+      </c>
       <c r="I53" s="23"/>
     </row>
     <row r="54" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2020,6 +2186,9 @@
       <c r="G54" s="15" t="s">
         <v>50</v>
       </c>
+      <c r="H54" t="s">
+        <v>64</v>
+      </c>
       <c r="I54" s="23"/>
     </row>
     <row r="55" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2044,6 +2213,9 @@
       <c r="G55" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="H55" t="s">
+        <v>64</v>
+      </c>
       <c r="I55" s="5"/>
     </row>
     <row r="56" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2068,6 +2240,9 @@
       <c r="G56" s="15" t="s">
         <v>33</v>
       </c>
+      <c r="H56" t="s">
+        <v>64</v>
+      </c>
       <c r="I56" s="8"/>
     </row>
     <row r="57" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2092,6 +2267,9 @@
       <c r="G57" s="15" t="s">
         <v>51</v>
       </c>
+      <c r="H57" t="s">
+        <v>64</v>
+      </c>
       <c r="I57" s="20"/>
     </row>
     <row r="58" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2116,6 +2294,9 @@
       <c r="G58" s="15" t="s">
         <v>22</v>
       </c>
+      <c r="H58" t="s">
+        <v>64</v>
+      </c>
       <c r="I58" s="5"/>
     </row>
     <row r="59" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2140,6 +2321,9 @@
       <c r="G59" s="15" t="s">
         <v>22</v>
       </c>
+      <c r="H59" t="s">
+        <v>64</v>
+      </c>
       <c r="I59" s="5"/>
     </row>
     <row r="60" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2164,6 +2348,9 @@
       <c r="G60" s="15" t="s">
         <v>34</v>
       </c>
+      <c r="H60" t="s">
+        <v>64</v>
+      </c>
       <c r="I60" s="8"/>
     </row>
     <row r="61" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2188,6 +2375,9 @@
       <c r="G61" s="15" t="s">
         <v>35</v>
       </c>
+      <c r="H61" t="s">
+        <v>64</v>
+      </c>
       <c r="I61" s="5"/>
     </row>
     <row r="62" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2212,6 +2402,9 @@
       <c r="G62" s="15" t="s">
         <v>31</v>
       </c>
+      <c r="H62" t="s">
+        <v>64</v>
+      </c>
       <c r="I62" s="5"/>
     </row>
     <row r="63" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2236,6 +2429,9 @@
       <c r="G63" s="15" t="s">
         <v>36</v>
       </c>
+      <c r="H63" t="s">
+        <v>64</v>
+      </c>
       <c r="I63" s="8"/>
     </row>
     <row r="64" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2260,6 +2456,9 @@
       <c r="G64" s="15" t="s">
         <v>37</v>
       </c>
+      <c r="H64" t="s">
+        <v>64</v>
+      </c>
       <c r="I64" s="8"/>
     </row>
     <row r="65" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2284,6 +2483,9 @@
       <c r="G65" s="20" t="s">
         <v>55</v>
       </c>
+      <c r="H65" t="s">
+        <v>64</v>
+      </c>
       <c r="I65" s="20"/>
     </row>
     <row r="66" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2308,6 +2510,9 @@
       <c r="G66" s="15" t="s">
         <v>51</v>
       </c>
+      <c r="H66" t="s">
+        <v>64</v>
+      </c>
       <c r="I66" s="8"/>
     </row>
     <row r="67" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2332,6 +2537,9 @@
       <c r="G67" s="15" t="s">
         <v>38</v>
       </c>
+      <c r="H67" t="s">
+        <v>64</v>
+      </c>
       <c r="I67" s="8"/>
     </row>
     <row r="68" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2356,6 +2564,9 @@
       <c r="G68" s="15" t="s">
         <v>34</v>
       </c>
+      <c r="H68" t="s">
+        <v>64</v>
+      </c>
       <c r="I68" s="8"/>
     </row>
     <row r="69" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2380,6 +2591,9 @@
       <c r="G69" s="15" t="s">
         <v>39</v>
       </c>
+      <c r="H69" t="s">
+        <v>64</v>
+      </c>
       <c r="I69" s="8"/>
     </row>
     <row r="70" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -2403,6 +2617,9 @@
       </c>
       <c r="G70" s="15" t="s">
         <v>56</v>
+      </c>
+      <c r="H70" t="s">
+        <v>64</v>
       </c>
       <c r="I70" s="5"/>
     </row>

--- a/FinalSheet.xlsx
+++ b/FinalSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nehakotha/GASP-Clean-Air-Fund/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C79A08-BCA3-F044-8390-49A5E4EF578C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2460930-DE11-E743-BC94-3E5522919E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6880" yWindow="760" windowWidth="23360" windowHeight="16300" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="64">
   <si>
     <t>Year</t>
   </si>
@@ -116,9 +116,6 @@
     <t>Solarize Allegheny</t>
   </si>
   <si>
-    <t>Southwest Pennsylvania Air Quality</t>
-  </si>
-  <si>
     <t>Pittsburgh</t>
   </si>
   <si>
@@ -137,21 +134,12 @@
     <t>enfoTech &amp; Consulting Inc.</t>
   </si>
   <si>
-    <t xml:space="preserve">Steel Rivers Council of Governments </t>
-  </si>
-  <si>
     <t>West Mifflin Borough</t>
   </si>
   <si>
     <t>Wilkinsburg Shade Tree Commission</t>
   </si>
   <si>
-    <t>Brackenridge</t>
-  </si>
-  <si>
-    <t>Pitcairn</t>
-  </si>
-  <si>
     <t>Munhall Borough</t>
   </si>
   <si>
@@ -231,6 +219,15 @@
   </si>
   <si>
     <t>…..</t>
+  </si>
+  <si>
+    <t>Steel Rivers Council of Governments</t>
+  </si>
+  <si>
+    <t>Air Quality Program+G15</t>
+  </si>
+  <si>
+    <t>Several small projects</t>
   </si>
 </sst>
 </file>
@@ -319,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -382,6 +379,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,13 +756,13 @@
         <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -780,13 +782,13 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -806,13 +808,13 @@
         <v>12</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -839,7 +841,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I4" s="21"/>
     </row>
@@ -860,13 +862,13 @@
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -887,13 +889,13 @@
         <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -920,7 +922,7 @@
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -943,11 +945,11 @@
       <c r="F8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="24" t="s">
         <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -968,13 +970,13 @@
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="24" t="s">
         <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -997,11 +999,11 @@
       <c r="F10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="24" t="s">
         <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I10" s="7"/>
     </row>
@@ -1024,11 +1026,11 @@
       <c r="F11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="24" t="s">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I11" s="7"/>
     </row>
@@ -1051,11 +1053,11 @@
       <c r="F12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="15" t="s">
-        <v>26</v>
+      <c r="G12" s="24" t="s">
+        <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I12" s="7"/>
     </row>
@@ -1076,13 +1078,13 @@
         <v>12</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1104,11 +1106,11 @@
       <c r="F14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="24" t="s">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -1129,13 +1131,13 @@
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="24" t="s">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -1162,7 +1164,7 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1188,7 +1190,7 @@
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -1212,10 +1214,10 @@
         <v>5</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I18" s="7"/>
     </row>
@@ -1242,7 +1244,7 @@
         <v>6</v>
       </c>
       <c r="H19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I19" s="22"/>
     </row>
@@ -1269,7 +1271,7 @@
         <v>6</v>
       </c>
       <c r="H20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -1296,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -1323,7 +1325,7 @@
         <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I22" s="4"/>
     </row>
@@ -1350,7 +1352,7 @@
         <v>6</v>
       </c>
       <c r="H23" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I23" s="4"/>
     </row>
@@ -1377,7 +1379,7 @@
         <v>6</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -1404,7 +1406,7 @@
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I25" s="4"/>
     </row>
@@ -1431,7 +1433,7 @@
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I26" s="5"/>
     </row>
@@ -1455,10 +1457,10 @@
         <v>5</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H27" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I27" s="8"/>
     </row>
@@ -1482,10 +1484,10 @@
         <v>5</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I28" s="5"/>
     </row>
@@ -1506,13 +1508,13 @@
         <v>12</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I29" s="5"/>
     </row>
@@ -1533,13 +1535,13 @@
         <v>12</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G30" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H30" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I30" s="8"/>
     </row>
@@ -1562,11 +1564,11 @@
       <c r="F31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="26" t="s">
         <v>4</v>
       </c>
       <c r="H31" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I31" s="4"/>
     </row>
@@ -1587,13 +1589,13 @@
         <v>12</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="H32" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I32" s="5"/>
     </row>
@@ -1614,13 +1616,13 @@
         <v>12</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="G33" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="H33" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I33" s="5"/>
     </row>
@@ -1643,11 +1645,11 @@
       <c r="F34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="24" t="s">
         <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I34" s="5"/>
     </row>
@@ -1671,10 +1673,10 @@
         <v>5</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="H35" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I35" s="5"/>
     </row>
@@ -1701,7 +1703,7 @@
         <v>6</v>
       </c>
       <c r="H36" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I36" s="5"/>
     </row>
@@ -1728,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="H37" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I37" s="8"/>
     </row>
@@ -1749,13 +1751,13 @@
         <v>12</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H38" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I38" s="5"/>
     </row>
@@ -1776,13 +1778,13 @@
         <v>12</v>
       </c>
       <c r="F39" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H39" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I39" s="5"/>
     </row>
@@ -1809,7 +1811,7 @@
         <v>6</v>
       </c>
       <c r="H40" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I40" s="5"/>
     </row>
@@ -1836,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="H41" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I41" s="5"/>
     </row>
@@ -1860,10 +1862,10 @@
         <v>5</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H42" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I42" s="5"/>
     </row>
@@ -1890,7 +1892,7 @@
         <v>6</v>
       </c>
       <c r="H43" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I43" s="5"/>
     </row>
@@ -1911,13 +1913,13 @@
         <v>8</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G44" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="24" t="s">
         <v>22</v>
       </c>
       <c r="H44" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I44" s="5"/>
     </row>
@@ -1938,13 +1940,13 @@
         <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="G45" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="H45" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I45" s="5"/>
     </row>
@@ -1965,13 +1967,13 @@
         <v>12</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G46" s="15" t="s">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="G46" s="24" t="s">
+        <v>30</v>
       </c>
       <c r="H46" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I46" s="5"/>
     </row>
@@ -1994,11 +1996,11 @@
       <c r="F47" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" s="24" t="s">
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I47" s="5"/>
     </row>
@@ -2021,11 +2023,11 @@
       <c r="F48" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="15" t="s">
+      <c r="G48" s="24" t="s">
         <v>3</v>
       </c>
       <c r="H48" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I48" s="5"/>
     </row>
@@ -2048,11 +2050,11 @@
       <c r="F49" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="26" t="s">
         <v>4</v>
       </c>
       <c r="H49" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I49" s="5"/>
     </row>
@@ -2075,11 +2077,11 @@
       <c r="F50" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G50" s="15" t="s">
+      <c r="G50" s="24" t="s">
         <v>3</v>
       </c>
       <c r="H50" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I50" s="5"/>
     </row>
@@ -2102,11 +2104,11 @@
       <c r="F51" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G51" s="15" t="s">
-        <v>32</v>
+      <c r="G51" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="H51" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I51" s="23"/>
     </row>
@@ -2127,13 +2129,13 @@
         <v>12</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H52" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I52" s="23"/>
     </row>
@@ -2154,13 +2156,13 @@
         <v>12</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H53" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I53" s="23"/>
     </row>
@@ -2181,13 +2183,13 @@
         <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H54" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I54" s="23"/>
     </row>
@@ -2208,13 +2210,13 @@
         <v>12</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H55" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I55" s="5"/>
     </row>
@@ -2235,13 +2237,13 @@
         <v>12</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="H56" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I56" s="8"/>
     </row>
@@ -2262,13 +2264,13 @@
         <v>12</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H57" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I57" s="20"/>
     </row>
@@ -2289,13 +2291,13 @@
         <v>12</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G58" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H58" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I58" s="5"/>
     </row>
@@ -2316,13 +2318,13 @@
         <v>12</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G59" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H59" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I59" s="5"/>
     </row>
@@ -2343,13 +2345,13 @@
         <v>12</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H60" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I60" s="8"/>
     </row>
@@ -2370,13 +2372,13 @@
         <v>12</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H61" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I61" s="5"/>
     </row>
@@ -2397,13 +2399,13 @@
         <v>12</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I62" s="5"/>
     </row>
@@ -2424,13 +2426,13 @@
         <v>12</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H63" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I63" s="8"/>
     </row>
@@ -2451,13 +2453,13 @@
         <v>12</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H64" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I64" s="8"/>
     </row>
@@ -2478,13 +2480,13 @@
         <v>12</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H65" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I65" s="20"/>
     </row>
@@ -2505,13 +2507,13 @@
         <v>12</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G66" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H66" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I66" s="8"/>
     </row>
@@ -2532,13 +2534,13 @@
         <v>12</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H67" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I67" s="8"/>
     </row>
@@ -2559,13 +2561,13 @@
         <v>12</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H68" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I68" s="8"/>
     </row>
@@ -2586,13 +2588,13 @@
         <v>12</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H69" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I69" s="8"/>
     </row>
@@ -2613,13 +2615,13 @@
         <v>15</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H70" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I70" s="5"/>
     </row>

--- a/FinalSheet.xlsx
+++ b/FinalSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nehakotha/GASP-Clean-Air-Fund/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2460930-DE11-E743-BC94-3E5522919E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F87560-EB1C-9145-A172-4DC9CE4603A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6880" yWindow="760" windowWidth="23360" windowHeight="16300" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
@@ -316,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -379,11 +379,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,7 +940,7 @@
       <c r="F8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="15" t="s">
         <v>9</v>
       </c>
       <c r="H8" t="s">
@@ -972,7 +967,7 @@
       <c r="F9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="H9" t="s">
@@ -999,7 +994,7 @@
       <c r="F10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="15" t="s">
         <v>25</v>
       </c>
       <c r="H10" t="s">
@@ -1026,7 +1021,7 @@
       <c r="F11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H11" t="s">
@@ -1053,7 +1048,7 @@
       <c r="F12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="15" t="s">
         <v>4</v>
       </c>
       <c r="H12" t="s">
@@ -1080,7 +1075,7 @@
       <c r="F13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H13" t="s">
@@ -1106,7 +1101,7 @@
       <c r="F14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H14" t="s">
@@ -1133,7 +1128,7 @@
       <c r="F15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="15" t="s">
         <v>7</v>
       </c>
       <c r="H15" t="s">
@@ -1564,7 +1559,7 @@
       <c r="F31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="G31" s="14" t="s">
         <v>4</v>
       </c>
       <c r="H31" t="s">
@@ -1591,7 +1586,7 @@
       <c r="F32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="25" t="s">
+      <c r="G32" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H32" t="s">
@@ -1618,7 +1613,7 @@
       <c r="F33" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H33" t="s">
@@ -1645,7 +1640,7 @@
       <c r="F34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="24" t="s">
+      <c r="G34" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H34" t="s">
@@ -1915,7 +1910,7 @@
       <c r="F44" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G44" s="24" t="s">
+      <c r="G44" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H44" t="s">
@@ -1942,7 +1937,7 @@
       <c r="F45" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G45" s="25" t="s">
+      <c r="G45" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H45" t="s">
@@ -1969,7 +1964,7 @@
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G46" s="24" t="s">
+      <c r="G46" s="15" t="s">
         <v>30</v>
       </c>
       <c r="H46" t="s">
@@ -1996,7 +1991,7 @@
       <c r="F47" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G47" s="24" t="s">
+      <c r="G47" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H47" t="s">
@@ -2023,7 +2018,7 @@
       <c r="F48" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="24" t="s">
+      <c r="G48" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H48" t="s">
@@ -2050,7 +2045,7 @@
       <c r="F49" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G49" s="26" t="s">
+      <c r="G49" s="14" t="s">
         <v>4</v>
       </c>
       <c r="H49" t="s">
@@ -2077,7 +2072,7 @@
       <c r="F50" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G50" s="24" t="s">
+      <c r="G50" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H50" t="s">
@@ -2104,7 +2099,7 @@
       <c r="F51" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G51" s="24" t="s">
+      <c r="G51" s="15" t="s">
         <v>31</v>
       </c>
       <c r="H51" t="s">

--- a/FinalSheet.xlsx
+++ b/FinalSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nehakotha/GASP-Clean-Air-Fund/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F87560-EB1C-9145-A172-4DC9CE4603A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA846D7-21B8-084C-89CD-7DADC50D572F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6880" yWindow="760" windowWidth="23360" windowHeight="16300" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
+    <workbookView xWindow="6880" yWindow="4440" windowWidth="23360" windowHeight="16300" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
   <sheets>
     <sheet name="FinalSheet" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="130">
   <si>
     <t>Year</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Allegheny County Parks Department</t>
   </si>
   <si>
-    <t>several small projects</t>
-  </si>
-  <si>
     <t>Lawrenceville, Chateau, Neville Island</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <t>Project Description</t>
   </si>
   <si>
-    <t>…..</t>
-  </si>
-  <si>
     <t>Steel Rivers Council of Governments</t>
   </si>
   <si>
@@ -228,6 +222,237 @@
   </si>
   <si>
     <t>Several small projects</t>
+  </si>
+  <si>
+    <t>To support the Carnegie Science Center Future Cities Competition ($2,000 per year for 2015 and 2016).</t>
+  </si>
+  <si>
+    <t>To plant trees on industrial properties in Lawrenceville, Chateau, and Neville Island; requested by Tree Pittsburgh</t>
+  </si>
+  <si>
+    <t>To fund an outreach campaign in response to the revisions to Article XXI Open Burning regulations; the campaign will discourage open burning educate on the health effects of wood smoke</t>
+  </si>
+  <si>
+    <t>To support the Northgate Asthma Initiative / continue to concentrate the Healthy Homes program on children in the Northgate School District, which has an elevated number of asthmatic children</t>
+  </si>
+  <si>
+    <t>For the purchase of solar panels to light parking lots and charge electric vehicles at CCAC campuses.</t>
+  </si>
+  <si>
+    <t>To fund 50% of an investment-grade audit for renovation of Clack Building #1 as a potential new location for Air Quality.</t>
+  </si>
+  <si>
+    <t>To fund six Student Conservation Association interns for city and county-based climate change group.</t>
+  </si>
+  <si>
+    <t>To fund a CMU air pollution modeling project aimed at predicting pollution dispersion in the Mon Valley and understanding air quality under multiple meteorological conditions and emissions scenarios.</t>
+  </si>
+  <si>
+    <t>To fund Solarize Allegheny, a project promoting residential solar energy options and contacts for contractors; project managed by SmartPower, a national non-profit marketing firm for clean energy.</t>
+  </si>
+  <si>
+    <t>Support for the ACHD project incentivizing owners of indoor fireplaces to convert to natural gas instead of burning wood (vendors would receive a rebate and purchasers would get a reduced price).</t>
+  </si>
+  <si>
+    <t>To support the Southwest Pennsylvania Air Quality Partnership Lawnmower Exchange Program ($12,000 per year for two years).</t>
+  </si>
+  <si>
+    <t>To support the Carnegie Science Center Future Cities Competition ($2,000 per year for the school years 2016-2017 and 2017-2018).</t>
+  </si>
+  <si>
+    <t>To launch a new initiative ("Air-Space") to generate air quality awareness and community capacity in high priority areas throughout the County; requested by G-tech, which will partner with ACHD.</t>
+  </si>
+  <si>
+    <t>To support the Pittsburgh Regional Science &amp; Engineering Fair ($2,500 per year for 2017, 2018, and 2019).</t>
+  </si>
+  <si>
+    <t>To support placing five Student Conservation Association Sustainability Fellows in environmental organizations.</t>
+  </si>
+  <si>
+    <t>For Air Quality Program software to assist in tracking all aspects of asbestos renovation and demolition activities and stationary source enforcement; this will replace a series of spreadsheets and old software.</t>
+  </si>
+  <si>
+    <t>To fund small projects ($10k - $30k) addressing air pollution public education projects and emission reduction projects, with $150,000 going to each of the two categories.</t>
+  </si>
+  <si>
+    <t>Air Quality Program 5% operations funding allocation for the year 2017.</t>
+  </si>
+  <si>
+    <t>Construction oversight services for the potential Clack Building #1 renovation project.</t>
+  </si>
+  <si>
+    <t>Air Quality Program 5% operations funding allocation for the year 2018.</t>
+  </si>
+  <si>
+    <t>Air Quality Program 5% operations funding allocation for the year 2019.</t>
+  </si>
+  <si>
+    <t>For Air Quality Program student interns for remainder of 2018 and for 2019.</t>
+  </si>
+  <si>
+    <t>For a part-time Clean Air Fund administrator for the Air Quality Program.</t>
+  </si>
+  <si>
+    <t>For the Air Quality Program to run a half-day workshop for municipal officials on air quality topics.</t>
+  </si>
+  <si>
+    <t>To provide professional and technical support on an as-needed basis to the Air Quality Program for case analysis, data and technical support, legal support, and medical and toxicology consulting.</t>
+  </si>
+  <si>
+    <t>To fund several small projects ($10k - $30k) addressing emission reductions.</t>
+  </si>
+  <si>
+    <t>To support UPMC Children’s Hospital and Pitt GSPH developing an asthma registry for children and adolescents for surveillance and management of asthma in Allegheny County.</t>
+  </si>
+  <si>
+    <t>To fund the Allegheny County Department of Parks for the purchase of 360 landscape trees, which will be planted at designated locations in the County's Parks over a two-year period.</t>
+  </si>
+  <si>
+    <t>County Department of Public Works: for solar lighting along Corrigan Dr. in South Park.</t>
+  </si>
+  <si>
+    <t>To support the Southwest Pennsylvania Air Quality Partnership lawnmower exchange program.</t>
+  </si>
+  <si>
+    <t>To support the Carnegie Science Center Future Cities competition  ($3,000 per year for 3 years).</t>
+  </si>
+  <si>
+    <t>Carnegie Science Center Pittsburgh Regional Science and Engineering fair support ($2,500 per year for 3 years).</t>
+  </si>
+  <si>
+    <t>Air Quality Program 5% operations funding allocation for the year 2020.</t>
+  </si>
+  <si>
+    <t>For air monitoring work and equipment supporting the Air Quality Program (relocation and upgrades at the Liberty Monitor site, back-up monitoring hardware, low-cost monitors, etc.).</t>
+  </si>
+  <si>
+    <t>To update / develop software the Air Quality Program enforcement and permitting staff use.</t>
+  </si>
+  <si>
+    <t>To plant 500 trees in various locations in the Carnegie and Churchill areas.</t>
+  </si>
+  <si>
+    <t>To plant 200 street trees in various low income areas.</t>
+  </si>
+  <si>
+    <t>Air Quality Program 5% operations funding allocation for the year 2021.</t>
+  </si>
+  <si>
+    <t>To fund an RFP that will ask community-based organizations to seek small grant to conduct outreach aimed at increasing participation / sign-ups / awareness around the County's Allegheny Alerts system; titled the "Air Ambassadors  Program"; ACHD will be overseeing community partners.</t>
+  </si>
+  <si>
+    <t>To design a health impact study covering the impacts of various pollutants involving ACHD in partnership with the University of Pittsburgh, Duquesne University, and Carnegie Mellon University.</t>
+  </si>
+  <si>
+    <t>Air Quality Program 5% operations funding allocation for the year 2022.</t>
+  </si>
+  <si>
+    <t>Engage over 1000 students from 20 different schools in the Mon Valley over 2 years. Plant 1250 trees with customized tree care plan for each school. Partnership with five school districts: Bethel Park, McKeesport, Woodland Hills, West Mifflin, and South Fayette.</t>
+  </si>
+  <si>
+    <t>Annual funding for three years.</t>
+  </si>
+  <si>
+    <t>Plant and maintain 75 trees.</t>
+  </si>
+  <si>
+    <t>Professional and technical support as needed for case analysis, technical expertise, legal support, and medical and toxicological consulting.</t>
+  </si>
+  <si>
+    <t>Hire a Clean Air and Environmental Health Fund Contract grant Administrator last year to help develop new processes and outreach strategies.</t>
+  </si>
+  <si>
+    <t>Provide guidelines for individual actions to reduce exposure to pollution, provide alerts on high pollution days, and ozone and particulate forecasting for three years ($25,000 per year for 2021, 2022, and 2023).</t>
+  </si>
+  <si>
+    <t>Purchase air monitoring equipment, cover sampling analysis costs, and provide lab analysis in support of the Air Quality Program conducting a study of odor and air toxics emissions and H2S in the Mon Valley.</t>
+  </si>
+  <si>
+    <t>Online portal to be created for air quality permitting and enforcement software.</t>
+  </si>
+  <si>
+    <t>Nine organizations each work on individual projects to educate municipalities in the Mon Valley about air quality and get residents to sign up for Allegheny Alerts.</t>
+  </si>
+  <si>
+    <t>Develop an air quality forecasting program for the Mon Valley Episode Rule.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S Analysis in Allegheny County with a focus within the Mon Valley.</t>
+    </r>
+  </si>
+  <si>
+    <t>Three years of annual funding to support the Carnegie Science Center's Pittsburgh Regional Future City Competition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace existing 2006 diesel powered street sweeper and purchase of an equivalent electric street sweeper and installation of electric vehicle charging station. </t>
+  </si>
+  <si>
+    <t>Replace existing 2016 diesel powered garbage truck and 2014 recycling truck and purchase of an equivalent electric garbage truck and recycling truck and installation of two electric vehicle charging stations at the borough's Public Works Department.</t>
+  </si>
+  <si>
+    <t>Plant 75 caliper, balled, and burlap trees on school grounds, community parks, and right of ways within Steel Valley School District.</t>
+  </si>
+  <si>
+    <t>Plant 75 caliper, balled, and burlap trees planted on school grounds, community parks, and right of ways within the Woodland Hills School District.</t>
+  </si>
+  <si>
+    <t>Decommission and replace existing 2007 diesel-powered refuse hauler truck and replace with electric rear-load garbage packer and installation of two electric vehicle charging stations and an electrical service upgrade at the vehicle site.</t>
+  </si>
+  <si>
+    <t>Plant and maintain 50 Trees in Wilkinsburg.</t>
+  </si>
+  <si>
+    <t>Plant and maintain 45 trees in Monongahela Valley communities.</t>
+  </si>
+  <si>
+    <t>Replace eleven gas powered pieces of municipal lawn equipment with electric models.</t>
+  </si>
+  <si>
+    <t>Replace 20 gas powered pieces of municipal lawn equipment with electric models.</t>
+  </si>
+  <si>
+    <t>Replace four gas powered pieces of municipal lawn equipment with electric models for the boroughs of Braddock, East Pittsburgh, North Braddock, and Rankin.</t>
+  </si>
+  <si>
+    <t>Replace a diesel powered street sweeper with an electric model.</t>
+  </si>
+  <si>
+    <t>Support the replacement of three diesel refuse trucks with electric models and charging infrastructure.</t>
+  </si>
+  <si>
+    <t>Funding to install a 1 MWh battery storage system as part of a multi-municipality effort to install solar and battery storage systems at municipal buildings in Allegheny County.</t>
+  </si>
+  <si>
+    <t>Funding to install a solar panel and battery storage system to offset the borough building's electrical usage and to provide backup power in the event of outages.</t>
+  </si>
+  <si>
+    <t>Funding to assist the installation of solar panels, green building technologies, and tree planting at their new municipal office building.</t>
   </si>
 </sst>
 </file>
@@ -237,7 +462,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -289,22 +514,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -312,11 +538,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -359,7 +594,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -378,6 +612,26 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -741,13 +995,13 @@
       <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -757,7 +1011,7 @@
         <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -770,10 +1024,10 @@
       <c r="C2" s="10">
         <v>4000</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -783,7 +1037,7 @@
         <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -796,20 +1050,20 @@
       <c r="C3" s="10">
         <v>50000</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>56</v>
+      <c r="E3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -823,10 +1077,10 @@
       <c r="C4" s="10">
         <v>225000</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -836,9 +1090,9 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="I4" s="20"/>
     </row>
     <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
@@ -850,20 +1104,20 @@
       <c r="C5" s="10">
         <v>337600</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -877,20 +1131,20 @@
       <c r="C6" s="10">
         <v>400000</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -904,10 +1158,10 @@
       <c r="C7" s="10">
         <v>450000</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -917,7 +1171,7 @@
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -931,10 +1185,10 @@
       <c r="C8" s="10">
         <v>78000</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -944,7 +1198,7 @@
         <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -958,10 +1212,10 @@
       <c r="C9" s="10">
         <v>717246</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -971,7 +1225,7 @@
         <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -985,10 +1239,10 @@
       <c r="C10" s="10">
         <v>180000</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -998,7 +1252,7 @@
         <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I10" s="7"/>
     </row>
@@ -1009,13 +1263,13 @@
       <c r="B11" s="12">
         <v>42431</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="18">
         <v>50000</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1025,7 +1279,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="I11" s="7"/>
     </row>
@@ -1036,13 +1290,13 @@
       <c r="B12" s="12">
         <v>42494</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <v>24000</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -1052,7 +1306,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I12" s="7"/>
     </row>
@@ -1063,13 +1317,13 @@
       <c r="B13" s="12">
         <v>42564</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="18">
         <v>4000</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1079,7 +1333,7 @@
         <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1089,23 +1343,23 @@
       <c r="B14" s="12">
         <v>43041</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>75900</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -1119,20 +1373,20 @@
       <c r="C15" s="10">
         <v>7500</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="27" t="s">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -1146,20 +1400,20 @@
       <c r="C16" s="10">
         <v>65000</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="27" t="s">
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1172,20 +1426,20 @@
       <c r="C17" s="10">
         <v>45000</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -1199,20 +1453,20 @@
       <c r="C18" s="10">
         <v>300000</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>63</v>
+      <c r="G18" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="H18" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I18" s="7"/>
     </row>
@@ -1226,22 +1480,22 @@
       <c r="C19" s="10">
         <v>558242</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H19" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="22"/>
+        <v>79</v>
+      </c>
+      <c r="I19" s="21"/>
     </row>
     <row r="20" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="11">
@@ -1253,20 +1507,20 @@
       <c r="C20" s="10">
         <v>66000</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H20" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -1280,20 +1534,20 @@
       <c r="C21" s="10">
         <v>579703</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -1307,20 +1561,20 @@
       <c r="C22" s="10">
         <v>546017</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="I22" s="4"/>
     </row>
@@ -1334,20 +1588,20 @@
       <c r="C23" s="10">
         <v>60000</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="I23" s="4"/>
     </row>
@@ -1361,20 +1615,20 @@
       <c r="C24" s="10">
         <v>24765</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H24" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -1388,20 +1642,20 @@
       <c r="C25" s="10">
         <v>15000</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="16" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I25" s="4"/>
     </row>
@@ -1415,20 +1669,20 @@
       <c r="C26" s="10">
         <v>120000</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="27" t="s">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="I26" s="5"/>
     </row>
@@ -1442,20 +1696,20 @@
       <c r="C27" s="10">
         <v>150000</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="16" t="s">
-        <v>63</v>
+      <c r="G27" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="H27" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="I27" s="8"/>
     </row>
@@ -1469,20 +1723,20 @@
       <c r="C28" s="10">
         <v>300000</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="28" t="s">
         <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="I28" s="5"/>
     </row>
@@ -1499,17 +1753,17 @@
       <c r="D29" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="27" t="s">
         <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="I29" s="5"/>
     </row>
@@ -1523,20 +1777,20 @@
       <c r="C30" s="10">
         <v>627100</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H30" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I30" s="8"/>
     </row>
@@ -1550,20 +1804,20 @@
       <c r="C31" s="10">
         <v>25000</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="29" t="s">
         <v>4</v>
       </c>
       <c r="H31" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="I31" s="4"/>
     </row>
@@ -1577,20 +1831,20 @@
       <c r="C32" s="10">
         <v>9000</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="30" t="s">
         <v>38</v>
       </c>
       <c r="H32" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="I32" s="5"/>
     </row>
@@ -1604,20 +1858,20 @@
       <c r="C33" s="10">
         <v>7500</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="30" t="s">
         <v>38</v>
       </c>
       <c r="H33" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="I33" s="5"/>
     </row>
@@ -1631,20 +1885,20 @@
       <c r="C34" s="10">
         <v>592822</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="H34" t="s">
-        <v>60</v>
+      <c r="H34" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="I34" s="5"/>
     </row>
@@ -1658,20 +1912,20 @@
       <c r="C35" s="10">
         <v>384000</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G35" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="G35" s="27" t="s">
         <v>60</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>95</v>
       </c>
       <c r="I35" s="5"/>
     </row>
@@ -1685,10 +1939,10 @@
       <c r="C36" s="10">
         <v>500000</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F36" s="2" t="s">
@@ -1697,8 +1951,8 @@
       <c r="G36" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H36" t="s">
-        <v>60</v>
+      <c r="H36" s="24" t="s">
+        <v>86</v>
       </c>
       <c r="I36" s="5"/>
     </row>
@@ -1712,10 +1966,10 @@
       <c r="C37" s="10">
         <v>210000</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="16" t="s">
         <v>19</v>
       </c>
       <c r="F37" s="2" t="s">
@@ -1724,8 +1978,8 @@
       <c r="G37" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H37" t="s">
-        <v>60</v>
+      <c r="H37" s="23" t="s">
+        <v>96</v>
       </c>
       <c r="I37" s="8"/>
     </row>
@@ -1739,10 +1993,10 @@
       <c r="C38" s="10">
         <v>59560</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F38" s="6" t="s">
@@ -1751,8 +2005,8 @@
       <c r="G38" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H38" t="s">
-        <v>60</v>
+      <c r="H38" s="23" t="s">
+        <v>97</v>
       </c>
       <c r="I38" s="5"/>
     </row>
@@ -1766,20 +2020,20 @@
       <c r="C39" s="10">
         <v>98000</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="23" t="s">
+      <c r="E39" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H39" t="s">
-        <v>60</v>
+      <c r="H39" s="23" t="s">
+        <v>98</v>
       </c>
       <c r="I39" s="5"/>
     </row>
@@ -1796,7 +2050,7 @@
       <c r="D40" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F40" s="2" t="s">
@@ -1805,8 +2059,8 @@
       <c r="G40" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H40" t="s">
-        <v>60</v>
+      <c r="H40" s="23" t="s">
+        <v>99</v>
       </c>
       <c r="I40" s="5"/>
     </row>
@@ -1820,10 +2074,10 @@
       <c r="C41" s="10">
         <v>200000</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
@@ -1832,8 +2086,8 @@
       <c r="G41" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H41" t="s">
-        <v>60</v>
+      <c r="H41" s="23" t="s">
+        <v>100</v>
       </c>
       <c r="I41" s="5"/>
     </row>
@@ -1847,10 +2101,10 @@
       <c r="C42" s="10">
         <v>30000</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F42" s="2" t="s">
@@ -1859,8 +2113,8 @@
       <c r="G42" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H42" t="s">
-        <v>60</v>
+      <c r="H42" s="23" t="s">
+        <v>101</v>
       </c>
       <c r="I42" s="5"/>
     </row>
@@ -1874,10 +2128,10 @@
       <c r="C43" s="10">
         <v>539125</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F43" s="2" t="s">
@@ -1886,8 +2140,8 @@
       <c r="G43" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H43" t="s">
-        <v>60</v>
+      <c r="H43" s="23" t="s">
+        <v>102</v>
       </c>
       <c r="I43" s="5"/>
     </row>
@@ -1901,7 +2155,7 @@
       <c r="C44" s="10">
         <v>99995</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="11" t="s">
@@ -1913,8 +2167,8 @@
       <c r="G44" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H44" t="s">
-        <v>60</v>
+      <c r="H44" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="I44" s="5"/>
     </row>
@@ -1928,10 +2182,10 @@
       <c r="C45" s="10">
         <v>15000</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
@@ -1940,8 +2194,8 @@
       <c r="G45" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H45" t="s">
-        <v>60</v>
+      <c r="H45" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="I45" s="5"/>
     </row>
@@ -1955,10 +2209,10 @@
       <c r="C46" s="10">
         <v>98000</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F46" s="6" t="s">
@@ -1967,8 +2221,8 @@
       <c r="G46" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H46" t="s">
-        <v>60</v>
+      <c r="H46" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="I46" s="5"/>
     </row>
@@ -1982,10 +2236,10 @@
       <c r="C47" s="10">
         <v>500000</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="2" t="s">
@@ -1994,8 +2248,8 @@
       <c r="G47" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H47" t="s">
-        <v>60</v>
+      <c r="H47" s="24" t="s">
+        <v>106</v>
       </c>
       <c r="I47" s="5"/>
     </row>
@@ -2009,10 +2263,10 @@
       <c r="C48" s="10">
         <v>55000</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F48" s="2" t="s">
@@ -2021,8 +2275,8 @@
       <c r="G48" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H48" t="s">
-        <v>60</v>
+      <c r="H48" s="24" t="s">
+        <v>107</v>
       </c>
       <c r="I48" s="5"/>
     </row>
@@ -2036,10 +2290,10 @@
       <c r="C49" s="10">
         <v>75000</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="16" t="s">
         <v>20</v>
       </c>
       <c r="F49" s="2" t="s">
@@ -2048,8 +2302,8 @@
       <c r="G49" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="H49" t="s">
-        <v>60</v>
+      <c r="H49" s="24" t="s">
+        <v>108</v>
       </c>
       <c r="I49" s="5"/>
     </row>
@@ -2063,10 +2317,10 @@
       <c r="C50" s="10">
         <v>340554</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="16" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="2" t="s">
@@ -2075,8 +2329,8 @@
       <c r="G50" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H50" t="s">
-        <v>60</v>
+      <c r="H50" s="24" t="s">
+        <v>109</v>
       </c>
       <c r="I50" s="5"/>
     </row>
@@ -2090,10 +2344,10 @@
       <c r="C51" s="10">
         <v>548725</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="16" t="s">
         <v>19</v>
       </c>
       <c r="F51" s="2" t="s">
@@ -2102,10 +2356,10 @@
       <c r="G51" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H51" t="s">
-        <v>60</v>
-      </c>
-      <c r="I51" s="23"/>
+      <c r="H51" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="I51" s="22"/>
     </row>
     <row r="52" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" s="11">
@@ -2117,22 +2371,22 @@
       <c r="C52" s="10">
         <v>200000</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G52" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I52" s="23"/>
+      <c r="G52" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="I52" s="22"/>
     </row>
     <row r="53" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="11">
@@ -2144,10 +2398,10 @@
       <c r="C53" s="13">
         <v>9941</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="3" t="s">
@@ -2156,12 +2410,12 @@
       <c r="G53" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H53" t="s">
-        <v>60</v>
-      </c>
-      <c r="I53" s="23"/>
-    </row>
-    <row r="54" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H53" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="I53" s="22"/>
+    </row>
+    <row r="54" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A54" s="11">
         <v>2021</v>
       </c>
@@ -2171,10 +2425,10 @@
       <c r="C54" s="13">
         <v>69956</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
@@ -2183,10 +2437,10 @@
       <c r="G54" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="H54" t="s">
-        <v>60</v>
-      </c>
-      <c r="I54" s="23"/>
+      <c r="H54" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="I54" s="22"/>
     </row>
     <row r="55" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="11">
@@ -2198,10 +2452,10 @@
       <c r="C55" s="10">
         <v>9000</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F55" s="2" t="s">
@@ -2210,8 +2464,8 @@
       <c r="G55" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H55" t="s">
-        <v>60</v>
+      <c r="H55" s="24" t="s">
+        <v>114</v>
       </c>
       <c r="I55" s="5"/>
     </row>
@@ -2225,20 +2479,20 @@
       <c r="C56" s="10">
         <v>750000</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="H56" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="H56" s="24" t="s">
+        <v>115</v>
       </c>
       <c r="I56" s="8"/>
     </row>
@@ -2255,7 +2509,7 @@
       <c r="D57" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F57" s="3" t="s">
@@ -2264,10 +2518,10 @@
       <c r="G57" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="H57" t="s">
-        <v>60</v>
-      </c>
-      <c r="I57" s="20"/>
+      <c r="H57" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="I57" s="19"/>
     </row>
     <row r="58" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="11">
@@ -2279,10 +2533,10 @@
       <c r="C58" s="10">
         <v>46000</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F58" s="6" t="s">
@@ -2291,8 +2545,8 @@
       <c r="G58" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H58" t="s">
-        <v>60</v>
+      <c r="H58" s="24" t="s">
+        <v>117</v>
       </c>
       <c r="I58" s="5"/>
     </row>
@@ -2306,10 +2560,10 @@
       <c r="C59" s="10">
         <v>46000</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F59" s="6" t="s">
@@ -2318,8 +2572,8 @@
       <c r="G59" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H59" t="s">
-        <v>60</v>
+      <c r="H59" s="24" t="s">
+        <v>118</v>
       </c>
       <c r="I59" s="5"/>
     </row>
@@ -2333,10 +2587,10 @@
       <c r="C60" s="10">
         <v>748339</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F60" s="6" t="s">
@@ -2345,8 +2599,8 @@
       <c r="G60" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H60" t="s">
-        <v>60</v>
+      <c r="H60" s="24" t="s">
+        <v>119</v>
       </c>
       <c r="I60" s="8"/>
     </row>
@@ -2360,10 +2614,10 @@
       <c r="C61" s="10">
         <v>46000</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F61" s="3" t="s">
@@ -2372,8 +2626,8 @@
       <c r="G61" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H61" t="s">
-        <v>60</v>
+      <c r="H61" s="24" t="s">
+        <v>120</v>
       </c>
       <c r="I61" s="5"/>
     </row>
@@ -2387,10 +2641,10 @@
       <c r="C62" s="10">
         <v>46000</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F62" s="3" t="s">
@@ -2399,8 +2653,8 @@
       <c r="G62" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H62" t="s">
-        <v>60</v>
+      <c r="H62" s="24" t="s">
+        <v>121</v>
       </c>
       <c r="I62" s="5"/>
     </row>
@@ -2414,10 +2668,10 @@
       <c r="C63" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F63" s="6" t="s">
@@ -2426,8 +2680,8 @@
       <c r="G63" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="H63" t="s">
-        <v>60</v>
+      <c r="H63" s="24" t="s">
+        <v>122</v>
       </c>
       <c r="I63" s="8"/>
     </row>
@@ -2441,10 +2695,10 @@
       <c r="C64" s="10">
         <v>43272</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F64" s="3" t="s">
@@ -2453,8 +2707,8 @@
       <c r="G64" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="H64" t="s">
-        <v>60</v>
+      <c r="H64" s="24" t="s">
+        <v>123</v>
       </c>
       <c r="I64" s="8"/>
     </row>
@@ -2468,22 +2722,22 @@
       <c r="C65" s="10">
         <v>75000</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G65" s="20" t="s">
+      <c r="G65" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H65" t="s">
-        <v>60</v>
-      </c>
-      <c r="I65" s="20"/>
+      <c r="H65" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="I65" s="19"/>
     </row>
     <row r="66" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="11">
@@ -2495,10 +2749,10 @@
       <c r="C66" s="10">
         <v>800000</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F66" s="3" t="s">
@@ -2507,8 +2761,8 @@
       <c r="G66" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="H66" t="s">
-        <v>60</v>
+      <c r="H66" s="24" t="s">
+        <v>125</v>
       </c>
       <c r="I66" s="8"/>
     </row>
@@ -2522,10 +2776,10 @@
       <c r="C67" s="10">
         <v>186789</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F67" s="3" t="s">
@@ -2534,8 +2788,8 @@
       <c r="G67" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H67" t="s">
-        <v>60</v>
+      <c r="H67" s="24" t="s">
+        <v>126</v>
       </c>
       <c r="I67" s="8"/>
     </row>
@@ -2549,10 +2803,10 @@
       <c r="C68" s="10">
         <v>997450</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E68" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F68" s="3" t="s">
@@ -2561,8 +2815,8 @@
       <c r="G68" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H68" t="s">
-        <v>60</v>
+      <c r="H68" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="I68" s="8"/>
     </row>
@@ -2576,10 +2830,10 @@
       <c r="C69" s="10">
         <v>1000000</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F69" s="3" t="s">
@@ -2588,8 +2842,8 @@
       <c r="G69" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H69" t="s">
-        <v>60</v>
+      <c r="H69" s="24" t="s">
+        <v>128</v>
       </c>
       <c r="I69" s="8"/>
     </row>
@@ -2603,10 +2857,10 @@
       <c r="C70" s="10">
         <v>500000</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="16" t="s">
         <v>15</v>
       </c>
       <c r="F70" s="3" t="s">
@@ -2615,8 +2869,8 @@
       <c r="G70" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="H70" t="s">
-        <v>60</v>
+      <c r="H70" s="26" t="s">
+        <v>129</v>
       </c>
       <c r="I70" s="5"/>
     </row>

--- a/FinalSheet.xlsx
+++ b/FinalSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nehakotha/GASP-Clean-Air-Fund/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA846D7-21B8-084C-89CD-7DADC50D572F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519046F9-05CE-0B4E-8E46-266529B21FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6880" yWindow="4440" windowWidth="23360" windowHeight="16300" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
+    <workbookView xWindow="6880" yWindow="1540" windowWidth="23360" windowHeight="16300" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
   <sheets>
     <sheet name="FinalSheet" sheetId="4" r:id="rId1"/>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>Bethel Park School District, McKeesport Area School District, Woodland Hills School District, West Mifflin Area School District, South Fayette School District</t>
-  </si>
-  <si>
-    <t>Monongahela Valley</t>
   </si>
   <si>
     <t>Georgia Institute of Technology</t>
@@ -428,9 +425,6 @@
     <t>Plant and maintain 50 Trees in Wilkinsburg.</t>
   </si>
   <si>
-    <t>Plant and maintain 45 trees in Monongahela Valley communities.</t>
-  </si>
-  <si>
     <t>Replace eleven gas powered pieces of municipal lawn equipment with electric models.</t>
   </si>
   <si>
@@ -453,6 +447,12 @@
   </si>
   <si>
     <t>Funding to assist the installation of solar panels, green building technologies, and tree planting at their new municipal office building.</t>
+  </si>
+  <si>
+    <t>Monongahela River Valley</t>
+  </si>
+  <si>
+    <t>Plant and maintain 45 trees in Monongahela River Valley communities.</t>
   </si>
 </sst>
 </file>
@@ -551,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -624,14 +624,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1011,7 +1003,7 @@
         <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1037,7 +1029,7 @@
         <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -1057,13 +1049,13 @@
         <v>12</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -1090,7 +1082,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I4" s="20"/>
     </row>
@@ -1111,13 +1103,13 @@
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -1138,13 +1130,13 @@
         <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -1171,7 +1163,7 @@
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -1198,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -1219,13 +1211,13 @@
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -1252,7 +1244,7 @@
         <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I10" s="7"/>
     </row>
@@ -1279,7 +1271,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I11" s="7"/>
     </row>
@@ -1306,7 +1298,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I12" s="7"/>
     </row>
@@ -1333,7 +1325,7 @@
         <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1355,11 +1347,11 @@
       <c r="F14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -1382,11 +1374,11 @@
       <c r="F15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="15" t="s">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -1409,11 +1401,11 @@
       <c r="F16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="15" t="s">
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17" x14ac:dyDescent="0.2">
@@ -1435,11 +1427,11 @@
       <c r="F17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -1462,11 +1454,11 @@
       <c r="F18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="27" t="s">
-        <v>61</v>
+      <c r="G18" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="H18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I18" s="7"/>
     </row>
@@ -1489,11 +1481,11 @@
       <c r="F19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I19" s="21"/>
     </row>
@@ -1516,11 +1508,11 @@
       <c r="F20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -1543,11 +1535,11 @@
       <c r="F21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G21" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -1570,11 +1562,11 @@
       <c r="F22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I22" s="4"/>
     </row>
@@ -1597,11 +1589,11 @@
       <c r="F23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="27" t="s">
+      <c r="G23" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I23" s="4"/>
     </row>
@@ -1624,11 +1616,11 @@
       <c r="F24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="G24" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -1651,11 +1643,11 @@
       <c r="F25" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="27" t="s">
+      <c r="G25" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I25" s="4"/>
     </row>
@@ -1678,11 +1670,11 @@
       <c r="F26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="27" t="s">
+      <c r="G26" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I26" s="5"/>
     </row>
@@ -1705,11 +1697,11 @@
       <c r="F27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="27" t="s">
-        <v>61</v>
+      <c r="G27" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="H27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I27" s="8"/>
     </row>
@@ -1732,11 +1724,11 @@
       <c r="F28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="28" t="s">
+      <c r="G28" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I28" s="5"/>
     </row>
@@ -1757,13 +1749,13 @@
         <v>12</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="15" t="s">
         <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I29" s="5"/>
     </row>
@@ -1784,13 +1776,13 @@
         <v>12</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="15" t="s">
         <v>3</v>
       </c>
       <c r="H30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I30" s="8"/>
     </row>
@@ -1813,11 +1805,11 @@
       <c r="F31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="G31" s="14" t="s">
         <v>4</v>
       </c>
       <c r="H31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I31" s="4"/>
     </row>
@@ -1840,11 +1832,11 @@
       <c r="F32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="30" t="s">
+      <c r="G32" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I32" s="5"/>
     </row>
@@ -1867,11 +1859,11 @@
       <c r="F33" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G33" s="30" t="s">
+      <c r="G33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I33" s="5"/>
     </row>
@@ -1894,11 +1886,11 @@
       <c r="F34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="27" t="s">
+      <c r="G34" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I34" s="5"/>
     </row>
@@ -1921,11 +1913,11 @@
       <c r="F35" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G35" s="27" t="s">
-        <v>60</v>
+      <c r="G35" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I35" s="5"/>
     </row>
@@ -1952,7 +1944,7 @@
         <v>6</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I36" s="5"/>
     </row>
@@ -1979,7 +1971,7 @@
         <v>6</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I37" s="8"/>
     </row>
@@ -2006,7 +1998,7 @@
         <v>28</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I38" s="5"/>
     </row>
@@ -2033,7 +2025,7 @@
         <v>29</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I39" s="5"/>
     </row>
@@ -2060,7 +2052,7 @@
         <v>6</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I40" s="5"/>
     </row>
@@ -2087,7 +2079,7 @@
         <v>6</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I41" s="5"/>
     </row>
@@ -2114,7 +2106,7 @@
         <v>42</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I42" s="5"/>
     </row>
@@ -2141,7 +2133,7 @@
         <v>6</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I43" s="5"/>
     </row>
@@ -2168,7 +2160,7 @@
         <v>22</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I44" s="5"/>
     </row>
@@ -2195,7 +2187,7 @@
         <v>38</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I45" s="5"/>
     </row>
@@ -2222,7 +2214,7 @@
         <v>30</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I46" s="5"/>
     </row>
@@ -2249,7 +2241,7 @@
         <v>3</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I47" s="5"/>
     </row>
@@ -2276,7 +2268,7 @@
         <v>3</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I48" s="5"/>
     </row>
@@ -2303,7 +2295,7 @@
         <v>4</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I49" s="5"/>
     </row>
@@ -2330,7 +2322,7 @@
         <v>3</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I50" s="5"/>
     </row>
@@ -2357,7 +2349,7 @@
         <v>31</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I51" s="22"/>
     </row>
@@ -2378,13 +2370,13 @@
         <v>12</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G52" s="27" t="s">
-        <v>61</v>
+        <v>128</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I52" s="22"/>
     </row>
@@ -2405,13 +2397,13 @@
         <v>12</v>
       </c>
       <c r="F53" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G53" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G53" s="14" t="s">
-        <v>45</v>
-      </c>
       <c r="H53" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I53" s="22"/>
     </row>
@@ -2432,13 +2424,13 @@
         <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I54" s="22"/>
     </row>
@@ -2465,7 +2457,7 @@
         <v>38</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I55" s="5"/>
     </row>
@@ -2486,13 +2478,13 @@
         <v>12</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I56" s="8"/>
     </row>
@@ -2513,13 +2505,13 @@
         <v>12</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I57" s="19"/>
     </row>
@@ -2546,7 +2538,7 @@
         <v>22</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I58" s="5"/>
     </row>
@@ -2573,7 +2565,7 @@
         <v>22</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I59" s="5"/>
     </row>
@@ -2600,7 +2592,7 @@
         <v>32</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I60" s="8"/>
     </row>
@@ -2621,13 +2613,13 @@
         <v>12</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G61" s="15" t="s">
         <v>33</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I61" s="5"/>
     </row>
@@ -2648,13 +2640,13 @@
         <v>12</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="G62" s="15" t="s">
         <v>30</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="I62" s="5"/>
     </row>
@@ -2675,13 +2667,13 @@
         <v>12</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I63" s="8"/>
     </row>
@@ -2702,13 +2694,13 @@
         <v>12</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I64" s="8"/>
     </row>
@@ -2729,13 +2721,13 @@
         <v>12</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I65" s="19"/>
     </row>
@@ -2756,13 +2748,13 @@
         <v>12</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G66" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I66" s="8"/>
     </row>
@@ -2789,7 +2781,7 @@
         <v>34</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I67" s="8"/>
     </row>
@@ -2816,7 +2808,7 @@
         <v>32</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I68" s="8"/>
     </row>
@@ -2843,7 +2835,7 @@
         <v>35</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I69" s="8"/>
     </row>
@@ -2864,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I70" s="5"/>
     </row>

--- a/FinalSheet.xlsx
+++ b/FinalSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nehakotha/GASP-Clean-Air-Fund/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519046F9-05CE-0B4E-8E46-266529B21FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57A8234-2C6E-8F4B-B071-489ADC48DB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6880" yWindow="1540" windowWidth="23360" windowHeight="16300" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
